--- a/Results/TestCases/XLSX/admin_TestCases.xlsx
+++ b/Results/TestCases/XLSX/admin_TestCases.xlsx
@@ -72,7 +72,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>SKIPPED</t>
+    <t>PASSED</t>
   </si>
   <si>
     <t>TC_ADMIN_02</t>
@@ -249,7 +249,7 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF5A6268"/>
+      <color rgb="FF107C41"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
@@ -268,7 +268,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E3E5"/>
+        <fgColor rgb="FFD1E7DD"/>
       </patternFill>
     </fill>
   </fills>

--- a/Results/TestCases/XLSX/admin_TestCases.xlsx
+++ b/Results/TestCases/XLSX/admin_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="100">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -58,15 +58,14 @@
     <t>Positive</t>
   </si>
   <si>
-    <t>OrangeHRM application is accessible</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Navigate to page
-2. Perform test actions
-3. Verify assertions</t>
-  </si>
-  <si>
-    <t>Test executes successfully and all assertions pass</t>
+    <t>The user is logged in to OrangeHRM with valid credentials and the Dashboard has loaded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Navigate to the 'PIM' module from the sidebar
+2. Navigate to the 'Admin' module from the sidebar</t>
+  </si>
+  <si>
+    <t>- The first row username should display the text 'testUsername'</t>
   </si>
   <si>
     <t>High</t>
@@ -81,18 +80,34 @@
     <t>Search user by username</t>
   </si>
   <si>
+    <t>1. Navigate to the 'Admin' module from the sidebar</t>
+  </si>
+  <si>
     <t>TC_ADMIN_03</t>
   </si>
   <si>
     <t>Update user details</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the 'Admin' module from the sidebar
+2. Click the edit button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- The first row username should display the text 'testUsername'
+- The Username field should have the value 'testUsername'
+- The user role dropdown should contain the text 'ESS'</t>
+  </si>
+  <si>
     <t>TC_ADMIN_04</t>
   </si>
   <si>
     <t>Verify user role displays correctly in search results</t>
   </si>
   <si>
+    <t xml:space="preserve">- The first row username should display the text 'testUsername'
+- The role text should equal 'ESS'</t>
+  </si>
+  <si>
     <t>Medium</t>
   </si>
   <si>
@@ -102,18 +117,35 @@
     <t>Verify Admin page has Add button visible</t>
   </si>
   <si>
+    <t>- The add button should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_06</t>
   </si>
   <si>
     <t>Delete existing user and cleanup employee</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the 'Admin' module from the sidebar
+2. Navigate to the 'PIM' module from the sidebar</t>
+  </si>
+  <si>
+    <t>- The table rows should have a count of '0'</t>
+  </si>
+  <si>
     <t>TC_ADMIN_07</t>
   </si>
   <si>
     <t>Verify resetting the search form clears username field</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the 'Admin' module from the sidebar
+2. Enter 'tempuser' into the search username input</t>
+  </si>
+  <si>
+    <t>- The search username input should have the value ''</t>
+  </si>
+  <si>
     <t>TC_ADMIN_08</t>
   </si>
   <si>
@@ -126,42 +158,63 @@
     <t>Verify Admin sub-menu bar contains User Management item</t>
   </si>
   <si>
+    <t>- The 'User Management' element should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_10</t>
   </si>
   <si>
     <t>Verify Job dropdown menu is visible in top navigation bar</t>
   </si>
   <si>
+    <t>- The 'Job' element should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_11</t>
   </si>
   <si>
     <t>Verify Organization dropdown menu is visible in top navigation bar</t>
   </si>
   <si>
+    <t>- The 'Organization' element should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_12</t>
   </si>
   <si>
     <t>Verify Qualifications dropdown menu is visible in top navigation bar</t>
   </si>
   <si>
+    <t>- The 'Qualifications' element should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_13</t>
   </si>
   <si>
     <t>Verify Nationalities tab item is visible in top navigation bar</t>
   </si>
   <si>
+    <t>- The 'Nationalities' element should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_14</t>
   </si>
   <si>
     <t>Verify Corporate Branding tab item is visible in top navigation bar</t>
   </si>
   <si>
+    <t>- The 'Corporate Branding' element should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_15</t>
   </si>
   <si>
     <t>Verify Configuration dropdown menu is visible in top navigation bar</t>
   </si>
   <si>
+    <t>- The 'Configuration' element should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_16</t>
   </si>
   <si>
@@ -171,58 +224,108 @@
     <t>Negative</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the 'Admin' module from the sidebar
+2. Click the add button
+3. Click the Save button</t>
+  </si>
+  <si>
+    <t>- The label element should display the text 'Required'</t>
+  </si>
+  <si>
     <t>TC_ADMIN_17</t>
   </si>
   <si>
     <t>Verify validation error on adding user with mismatched confirm password</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the 'Admin' module from the sidebar
+2. Click the add button
+3. Enter 'Password123' into the Password field
+4. Enter 'Different123' into the confirm password input</t>
+  </si>
+  <si>
+    <t>- The 'Confirm Password' element should display the text 'Passwords do not match'</t>
+  </si>
+  <si>
     <t>TC_ADMIN_18</t>
   </si>
   <si>
     <t>Verify autocomplete dropdown is hidden by default</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the 'Admin' module from the sidebar
+2. Click the add button</t>
+  </si>
+  <si>
+    <t>- The autocomplete dropdown should not be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_19</t>
   </si>
   <si>
     <t>Verify cancel button returns to user grid page</t>
   </si>
   <si>
+    <t xml:space="preserve">1. Navigate to the 'Admin' module from the sidebar
+2. Click the add button
+3. Click the oxd button  ghost element</t>
+  </si>
+  <si>
+    <t>- The page.url() should contain '/admin/viewSystemUsers'</t>
+  </si>
+  <si>
     <t>TC_ADMIN_20</t>
   </si>
   <si>
     <t>Verify select all checkbox is visible on table header</t>
   </si>
   <si>
+    <t>- The select all checkbox should be present</t>
+  </si>
+  <si>
     <t>TC_ADMIN_21</t>
   </si>
   <si>
     <t>Verify row checkbox can be hovered and clicked</t>
   </si>
   <si>
+    <t>- The row checkbox should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_22</t>
   </si>
   <si>
     <t>Verify records count display text exists above table</t>
   </si>
   <si>
+    <t>- The records text should be visible</t>
+  </si>
+  <si>
     <t>TC_ADMIN_23</t>
   </si>
   <si>
     <t>Verify Admin breadcrumb title contains User Management</t>
   </si>
   <si>
+    <t>- The breadcrumb should contain the text 'User Management'</t>
+  </si>
+  <si>
     <t>TC_ADMIN_24</t>
   </si>
   <si>
     <t>Verify table column headers Username, User Role, Employee Name, Status, Actions exist</t>
   </si>
   <si>
+    <t>- The col should be present</t>
+  </si>
+  <si>
     <t>TC_ADMIN_25</t>
   </si>
   <si>
     <t>Verify search button tag name is button</t>
+  </si>
+  <si>
+    <t>- The tag name should equal 'button'</t>
   </si>
 </sst>
 </file>
@@ -766,7 +869,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>17</v>
@@ -780,7 +883,7 @@
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -789,22 +892,22 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
@@ -815,7 +918,7 @@
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -824,25 +927,25 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -850,7 +953,7 @@
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -859,25 +962,25 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>19</v>
@@ -885,7 +988,7 @@
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -894,25 +997,25 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>19</v>
@@ -920,7 +1023,7 @@
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -929,25 +1032,25 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -955,7 +1058,7 @@
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -964,25 +1067,25 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>19</v>
@@ -990,7 +1093,7 @@
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -999,25 +1102,25 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>19</v>
@@ -1025,7 +1128,7 @@
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1034,25 +1137,25 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>19</v>
@@ -1060,7 +1163,7 @@
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1069,25 +1172,25 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1095,7 +1198,7 @@
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1104,25 +1207,25 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>19</v>
@@ -1130,7 +1233,7 @@
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1139,25 +1242,25 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>17</v>
+        <v>58</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>19</v>
@@ -1165,7 +1268,7 @@
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1174,25 +1277,25 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>19</v>
@@ -1200,7 +1303,7 @@
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1209,25 +1312,25 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>19</v>
@@ -1235,7 +1338,7 @@
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1244,25 +1347,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>19</v>
@@ -1270,7 +1373,7 @@
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1279,25 +1382,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>19</v>
@@ -1305,7 +1408,7 @@
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1314,25 +1417,25 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>16</v>
+        <v>76</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>17</v>
+        <v>77</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K19" s="3" t="s">
         <v>19</v>
@@ -1340,7 +1443,7 @@
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1349,25 +1452,25 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>19</v>
@@ -1375,7 +1478,7 @@
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1384,25 +1487,25 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>84</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>19</v>
@@ -1410,7 +1513,7 @@
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1419,25 +1522,25 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>17</v>
+        <v>87</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>19</v>
@@ -1445,7 +1548,7 @@
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1454,25 +1557,25 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>19</v>
@@ -1480,7 +1583,7 @@
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1489,25 +1592,25 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>19</v>
@@ -1515,7 +1618,7 @@
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1524,25 +1627,25 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>17</v>
+        <v>96</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>19</v>
@@ -1550,7 +1653,7 @@
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1559,25 +1662,25 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>19</v>

--- a/Results/TestCases/XLSX/admin_TestCases.xlsx
+++ b/Results/TestCases/XLSX/admin_TestCases.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="101">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -71,7 +71,7 @@
     <t>High</t>
   </si>
   <si>
-    <t>PASSED</t>
+    <t>FAILED</t>
   </si>
   <si>
     <t>TC_ADMIN_02</t>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>1. Navigate to the 'Admin' module from the sidebar</t>
+  </si>
+  <si>
+    <t>SKIPPED</t>
   </si>
   <si>
     <t>TC_ADMIN_03</t>
@@ -332,7 +335,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -352,12 +355,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF107C41"/>
+      <color rgb="FFA51D24"/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF5A6268"/>
       <sz val="10"/>
       <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,7 +380,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD1E7DD"/>
+        <fgColor rgb="FFF8D7DA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2E3E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -413,7 +427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -422,6 +436,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -877,13 +894,13 @@
       <c r="J3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
@@ -892,33 +909,33 @@
         <v>12</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
+      <c r="K4" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="5" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -927,13 +944,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>15</v>
@@ -942,18 +959,18 @@
         <v>22</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
@@ -962,13 +979,13 @@
         <v>12</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>15</v>
@@ -977,18 +994,18 @@
         <v>22</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
@@ -997,33 +1014,33 @@
         <v>12</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="8" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
@@ -1032,33 +1049,33 @@
         <v>12</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="9" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
@@ -1067,13 +1084,13 @@
         <v>12</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>15</v>
@@ -1082,18 +1099,18 @@
         <v>22</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
@@ -1102,13 +1119,13 @@
         <v>12</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>15</v>
@@ -1117,18 +1134,18 @@
         <v>22</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>12</v>
@@ -1137,13 +1154,13 @@
         <v>12</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>15</v>
@@ -1152,18 +1169,18 @@
         <v>22</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>12</v>
@@ -1172,13 +1189,13 @@
         <v>12</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>15</v>
@@ -1187,18 +1204,18 @@
         <v>22</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="13" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>12</v>
@@ -1207,13 +1224,13 @@
         <v>12</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>15</v>
@@ -1222,18 +1239,18 @@
         <v>22</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="14" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
@@ -1242,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>15</v>
@@ -1257,18 +1274,18 @@
         <v>22</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="15" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>12</v>
@@ -1277,13 +1294,13 @@
         <v>12</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>15</v>
@@ -1292,18 +1309,18 @@
         <v>22</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="16" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
@@ -1312,13 +1329,13 @@
         <v>12</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>15</v>
@@ -1327,18 +1344,18 @@
         <v>22</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
@@ -1347,33 +1364,33 @@
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="G17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="18" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
@@ -1382,33 +1399,33 @@
         <v>12</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="19" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
@@ -1417,33 +1434,33 @@
         <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="20" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>12</v>
@@ -1452,33 +1469,33 @@
         <v>12</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="21" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
@@ -1487,13 +1504,13 @@
         <v>12</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>15</v>
@@ -1502,18 +1519,18 @@
         <v>22</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
@@ -1522,13 +1539,13 @@
         <v>12</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>15</v>
@@ -1537,18 +1554,18 @@
         <v>22</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="23" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
@@ -1557,13 +1574,13 @@
         <v>12</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>15</v>
@@ -1572,18 +1589,18 @@
         <v>22</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="24" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>12</v>
@@ -1592,13 +1609,13 @@
         <v>12</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>15</v>
@@ -1607,18 +1624,18 @@
         <v>22</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="25" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>12</v>
@@ -1627,13 +1644,13 @@
         <v>12</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>15</v>
@@ -1642,18 +1659,18 @@
         <v>22</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="26" ht="35" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>12</v>
@@ -1662,13 +1679,13 @@
         <v>12</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>15</v>
@@ -1677,13 +1694,13 @@
         <v>22</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
+        <v>31</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
